--- a/data/bharath_jobs.xlsx
+++ b/data/bharath_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2271,7 +2271,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>d70c946def9277264592</t>
+          <t>d1ab00d5d0d0d90c8b44</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=7&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Engineer&amp;jobAge=248&amp;brelb=15&amp;scr=29.636913&amp;bscr=29.636913&amp;aq=-6518233495804833193&amp;elckey=960063128795572038</t>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=7&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Engineer&amp;jobAge=250&amp;brelb=15&amp;scr=29.151548&amp;bscr=29.151548&amp;aq=3998661454198801811&amp;elckey=-9057002434667722772</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2342,7 +2342,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8ad9de3658433ac69f42</t>
+          <t>7946f3a25937b90ec0dc</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=9&amp;rgn=55126&amp;cid=18943&amp;ckey=DevOps+Engineer&amp;jobAge=248&amp;brelb=15&amp;scr=30.79467&amp;bscr=30.79467&amp;aq=9055204443953461499&amp;elckey=6081379725337038057</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=DevOps+Engineer&amp;rgn=55126&amp;pos=9&amp;groupId=40147&amp;elckey=6217545559936752959&amp;p=1&amp;aq=8301209526903046470&amp;cid=18943&amp;jobAge=250&amp;brelb=15&amp;bscr=30.21451&amp;scr=30.21451</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2413,7 +2413,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>e68769aa9f84bc682233</t>
+          <t>3db177a74114cca1bfb7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=1&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+%26+DevOps+Engineer&amp;jobAge=248&amp;brelb=15&amp;scr=72.21045&amp;bscr=72.21045&amp;aq=-7182674109276387699&amp;elckey=6256717598117911016</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=Cloud+%26+DevOps+Engineer&amp;rgn=55126&amp;pos=1&amp;groupId=-1348710226&amp;elckey=-3760347965345383794&amp;p=1&amp;aq=-8953706846235333145&amp;cid=18943&amp;jobAge=250&amp;brelb=15&amp;bscr=70.875305&amp;scr=70.875305</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2484,7 +2484,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9d65346cdda8dadb2acc</t>
+          <t>26a4a76ed3502a774417</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=Cloud+Automation+Engineer&amp;rgn=55126&amp;pos=15&amp;groupId=-1567491464&amp;elckey=8748384845333706512&amp;p=1&amp;aq=-1503318778482598646&amp;cid=18943&amp;jobAge=248&amp;brelb=15&amp;bscr=30.006271&amp;scr=30.006271</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=Cloud+Automation+Engineer&amp;rgn=55126&amp;pos=17&amp;groupId=-1567491464&amp;elckey=-1268680718129588298&amp;p=1&amp;aq=2956090603363316027&amp;cid=18943&amp;jobAge=250&amp;brelb=15&amp;bscr=28.95188&amp;scr=28.95188</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2555,7 +2555,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6646b46cb5dfdcbcacee</t>
+          <t>0103e3c3afbee1f9622e</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-2667151008715974299?p=1&amp;pos=3&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=296&amp;brelb=15&amp;scr=117.28989&amp;bscr=117.28989&amp;aq=8312648200676879506&amp;elckey=4656431235604478715</t>
+          <t>https://jooble.org/desc/-2667151008715974299?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=3&amp;groupId=41745&amp;elckey=4792597070204193617&amp;p=1&amp;aq=-7335612189008304362&amp;cid=18943&amp;jobAge=298&amp;brelb=15&amp;bscr=115.879395&amp;scr=115.879395</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2626,7 +2626,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>418741cecc8bb7679895</t>
+          <t>bc8d665e6525691c76bc</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=8&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=656&amp;brelb=15&amp;scr=57.504597&amp;bscr=57.504597&amp;aq=8312648200676879506&amp;elckey=4656431235604478715</t>
+          <t>https://jooble.org/desc/3479600901415878407?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=8&amp;groupId=41745&amp;elckey=4792597070204193617&amp;p=1&amp;aq=-7335612189008304362&amp;cid=18943&amp;jobAge=658&amp;brelb=15&amp;bscr=56.83042&amp;scr=56.83042</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2702,7 +2702,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ec7cc1fb711553f8743a</t>
+          <t>4ef9e6cb23008988eb00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=9&amp;groupId=41745&amp;elckey=4656431235604478715&amp;p=1&amp;aq=8312648200676879506&amp;cid=18943&amp;jobAge=248&amp;brelb=15&amp;bscr=56.97019&amp;scr=56.97019</t>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=9&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=250&amp;brelb=15&amp;scr=56.829937&amp;bscr=56.829937&amp;aq=-7335612189008304362&amp;elckey=4792597070204193617</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2773,7 +2773,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>641a95371266d06c27f2</t>
+          <t>8a0c99a0131d702dd4bc</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=Infrastructure+Engineer&amp;rgn=55126&amp;pos=11&amp;groupId=43952&amp;elckey=5250859406466461135&amp;p=1&amp;aq=-3008065660752743052&amp;cid=18943&amp;jobAge=248&amp;brelb=15&amp;bscr=27.654163&amp;scr=27.654163</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=Infrastructure+Engineer&amp;rgn=55126&amp;pos=10&amp;groupId=43952&amp;elckey=-4766206156996833675&amp;p=1&amp;aq=2566503557959261259&amp;cid=18943&amp;jobAge=250&amp;brelb=15&amp;bscr=27.29295&amp;scr=27.29295</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-09-03 14:51:48</t>
+          <t>2026-09-03 16:29:49</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">

--- a/data/bharath_jobs.xlsx
+++ b/data/bharath_jobs.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2271,7 +2271,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>d1ab00d5d0d0d90c8b44</t>
+          <t>8a6c9c7c983e844faa64</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=7&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Engineer&amp;jobAge=250&amp;brelb=15&amp;scr=29.151548&amp;bscr=29.151548&amp;aq=3998661454198801811&amp;elckey=-9057002434667722772</t>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=11&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+Engineer&amp;jobAge=260&amp;brelb=15&amp;scr=28.932817&amp;bscr=28.932817&amp;aq=7450345883423236858&amp;elckey=3525813309626419305</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2342,7 +2342,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7946f3a25937b90ec0dc</t>
+          <t>9f60b7c386e6eb483ae1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=DevOps+Engineer&amp;rgn=55126&amp;pos=9&amp;groupId=40147&amp;elckey=6217545559936752959&amp;p=1&amp;aq=8301209526903046470&amp;cid=18943&amp;jobAge=250&amp;brelb=15&amp;bscr=30.21451&amp;scr=30.21451</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=DevOps+Engineer&amp;rgn=55126&amp;pos=9&amp;groupId=40147&amp;elckey=-6062335632225232796&amp;p=1&amp;aq=4699623705544958912&amp;cid=18943&amp;jobAge=260&amp;brelb=15&amp;bscr=30.928972&amp;scr=30.928972</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2413,7 +2413,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3db177a74114cca1bfb7</t>
+          <t>f0af18f7d68f9f7e0e03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=Cloud+%26+DevOps+Engineer&amp;rgn=55126&amp;pos=1&amp;groupId=-1348710226&amp;elckey=-3760347965345383794&amp;p=1&amp;aq=-8953706846235333145&amp;cid=18943&amp;jobAge=250&amp;brelb=15&amp;bscr=70.875305&amp;scr=70.875305</t>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=1&amp;rgn=55126&amp;cid=18943&amp;ckey=Cloud+%26+DevOps+Engineer&amp;jobAge=260&amp;brelb=15&amp;scr=71.407234&amp;bscr=71.407234&amp;aq=-6287276268388984128&amp;elckey=4172886658288941443</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2484,7 +2484,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26a4a76ed3502a774417</t>
+          <t>a39f7019d4fa08d90b8f</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=Cloud+Automation+Engineer&amp;rgn=55126&amp;pos=17&amp;groupId=-1567491464&amp;elckey=-1268680718129588298&amp;p=1&amp;aq=2956090603363316027&amp;cid=18943&amp;jobAge=250&amp;brelb=15&amp;bscr=28.95188&amp;scr=28.95188</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=Cloud+Automation+Engineer&amp;rgn=55126&amp;pos=19&amp;groupId=-1567491464&amp;elckey=-7132609047544997837&amp;p=1&amp;aq=-1130542334748574228&amp;cid=18943&amp;jobAge=260&amp;brelb=15&amp;bscr=28.932573&amp;scr=28.932573</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2555,7 +2555,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0103e3c3afbee1f9622e</t>
+          <t>54edd5ca852e9dd2a998</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-2667151008715974299?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=3&amp;groupId=41745&amp;elckey=4792597070204193617&amp;p=1&amp;aq=-7335612189008304362&amp;cid=18943&amp;jobAge=298&amp;brelb=15&amp;bscr=115.879395&amp;scr=115.879395</t>
+          <t>https://jooble.org/desc/-2667151008715974299?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=4&amp;groupId=41745&amp;elckey=-7487284121957792138&amp;p=1&amp;aq=1633849208674161106&amp;cid=18943&amp;jobAge=308&amp;brelb=15&amp;bscr=116.634026&amp;scr=116.634026</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2626,7 +2626,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bc8d665e6525691c76bc</t>
+          <t>95f452bf18cf901bd041</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/3479600901415878407?ckey=Backend+Engineer&amp;rgn=55126&amp;pos=8&amp;groupId=41745&amp;elckey=4792597070204193617&amp;p=1&amp;aq=-7335612189008304362&amp;cid=18943&amp;jobAge=658&amp;brelb=15&amp;bscr=56.83042&amp;scr=56.83042</t>
+          <t>https://jooble.org/away/3479600901415878407?p=1&amp;pos=8&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=668&amp;brelb=15&amp;scr=57.15673&amp;bscr=57.15673&amp;aq=1633849208674161106&amp;elckey=-7487284121957792138</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2702,7 +2702,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4ef9e6cb23008988eb00</t>
+          <t>23ccf67b33d27868c81c</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=9&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=250&amp;brelb=15&amp;scr=56.829937&amp;bscr=56.829937&amp;aq=-7335612189008304362&amp;elckey=4792597070204193617</t>
+          <t>https://jooble.org/away/-5777134769781578189?p=1&amp;pos=9&amp;rgn=55126&amp;cid=18943&amp;ckey=Backend+Engineer&amp;jobAge=260&amp;brelb=15&amp;scr=56.75284&amp;bscr=56.75284&amp;aq=1633849208674161106&amp;elckey=-7487284121957792138</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2773,7 +2773,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8a0c99a0131d702dd4bc</t>
+          <t>db78942cf8ebdd91c383</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://jooble.org/desc/-5777134769781578189?ckey=Infrastructure+Engineer&amp;rgn=55126&amp;pos=10&amp;groupId=43952&amp;elckey=-4766206156996833675&amp;p=1&amp;aq=2566503557959261259&amp;cid=18943&amp;jobAge=250&amp;brelb=15&amp;bscr=27.29295&amp;scr=27.29295</t>
+          <t>https://jooble.org/desc/-5777134769781578189?ckey=Infrastructure+Engineer&amp;rgn=55126&amp;pos=10&amp;groupId=43952&amp;elckey=7816609587297308402&amp;p=1&amp;aq=5328271980829752205&amp;cid=18943&amp;jobAge=260&amp;brelb=15&amp;bscr=27.547806&amp;scr=27.547806</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-09-03 16:29:49</t>
+          <t>2026-09-04 02:27:49</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">

--- a/data/bharath_jobs.xlsx
+++ b/data/bharath_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,77 @@
           <t>Notes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>70da7ba9e567970fee1f</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Job Description: Java Full Stack Developer (React.js &amp; Azure) Job Summary We are seeking a highly skilled Java Full Stack Developer with proven expertise in building robust backend services using Java/Spring Boot , developing dynamic user interfaces with React.js , and deploying scalable application</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5876028775?se=bFwBuGWs8RGLWNueJPgGLw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=856CDB2255452987D90E6BE969C4268474A3A29E</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:48:25</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:48:25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>61b0829734ac4f5c1943</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>skill:Java, skill:Spring Boot</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/bharath_jobs.xlsx
+++ b/data/bharath_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,77 +492,6 @@
           <t>Notes</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>70da7ba9e567970fee1f</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Java Software Engineer</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Job Description: Java Full Stack Developer (React.js &amp; Azure) Job Summary We are seeking a highly skilled Java Full Stack Developer with proven expertise in building robust backend services using Java/Spring Boot , developing dynamic user interfaces with React.js , and deploying scalable application</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://www.adzuna.in/land/ad/5876028775?se=bFwBuGWs8RGLWNueJPgGLw&amp;utm_medium=api&amp;utm_source=447522e9&amp;v=856CDB2255452987D90E6BE969C4268474A3A29E</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>adzuna</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-09-09 15:48:25</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-09-09 15:48:25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>61b0829734ac4f5c1943</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>20</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>skill:Java, skill:Spring Boot</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
